--- a/Data/EXCEL/Transfer/salemon/20240711/6625-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6625-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF6565B-8443-4261-AC86-D803B4596685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E14B1B66-1829-43E5-9326-68EEC209B5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{6F9600B1-476D-49C6-951B-6F1FF3327E68}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{AB06C091-3F63-40CD-BA20-627AC3220B8B}"/>
   </bookViews>
   <sheets>
     <sheet name="6625-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,25 +1261,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC83E450-3495-418B-AFBE-65EAD7B11EDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE1140A-0F0A-486E-B880-6F01C936FBAC}">
   <dimension ref="A1:Q189"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1388,7 +1388,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1427,7 +1427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>162.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>96.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>142.19999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>171.6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>196.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>207.2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>206.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>160.19999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>128.80000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>-36.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>-6.87</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>-3.87</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>-4.59</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>100.2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>74.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>-35.700000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>-26.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>-41.1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>-45.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>-59.6</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>-59.2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>-54.4</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>-49.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>-46.2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>-16.7</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>-29.6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>-31.6</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>-31.2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>-6.26</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>-6.92</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>-2.66</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>-7.93</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>106.8</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6197,477 +6197,477 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>42736</v>
       </c>
